--- a/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 58 D20 Spring 2024 24GE02I94 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 58 D20 Spring 2024 24GE02I94 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccm243\OneDrive - Cornell University\Desktop\GLNPO Counts\2024\Spring\Erie\d20\Zoops\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25E6D63-727B-455B-BCB8-95F0B72DA666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2AFBFE-C769-402B-9CD4-3F9C2C60EB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B0F09A55-7FE2-4F8B-BC99-A4197BADBE21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B0F09A55-7FE2-4F8B-BC99-A4197BADBE21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$304</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1571" r:id="rId2"/>
+    <pivotCache cacheId="46" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -6737,7 +6737,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE9FF85D-8734-4452-A61A-4E1814ED80B9}" name="PivotTable1" cacheId="1571" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE9FF85D-8734-4452-A61A-4E1814ED80B9}" name="PivotTable1" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:W26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -7207,20 +7207,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5C814A-1296-4077-954B-019A2A86A661}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W304"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" customWidth="1"/>
-    <col min="20" max="20" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.81640625" customWidth="1"/>
-    <col min="23" max="23" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" customWidth="1"/>
+    <col min="20" max="20" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.77734375" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7276,7 +7277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -7329,7 +7330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7388,7 +7389,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7453,7 +7454,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7518,7 +7519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -7583,7 +7584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7645,7 +7646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -7710,7 +7711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -7772,7 +7773,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7837,7 +7838,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -7902,7 +7903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -7967,7 +7968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -8032,7 +8033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -8097,7 +8098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -8162,7 +8163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -8224,7 +8225,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -8286,7 +8287,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -8348,7 +8349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -8413,7 +8414,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -8478,7 +8479,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -8543,7 +8544,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -8608,7 +8609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -8673,7 +8674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -8738,7 +8739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -8803,7 +8804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -8868,7 +8869,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -8921,7 +8922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -8983,7 +8984,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -9043,7 +9044,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -9105,7 +9106,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -9165,7 +9166,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -9225,7 +9226,7 @@
       </c>
       <c r="V32" s="15"/>
     </row>
-    <row r="33" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:22" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -9285,7 +9286,7 @@
       </c>
       <c r="V33" s="15"/>
     </row>
-    <row r="34" spans="1:22" ht="16" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -9343,7 +9344,7 @@
       <c r="U34" s="14"/>
       <c r="V34" s="15"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -9449,7 +9450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -9505,7 +9506,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -9558,7 +9559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -9611,7 +9612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -9664,7 +9665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -9717,7 +9718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -9770,7 +9771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -9823,7 +9824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -9876,7 +9877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -9929,7 +9930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -9982,7 +9983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -10035,7 +10036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -10088,7 +10089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -10141,7 +10142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -10194,7 +10195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -10247,7 +10248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -10300,7 +10301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -10353,7 +10354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -10406,7 +10407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -10459,7 +10460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -10512,7 +10513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -10565,7 +10566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -10621,7 +10622,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -10674,7 +10675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -10727,7 +10728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -10783,7 +10784,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -10836,7 +10837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -10889,7 +10890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -10942,7 +10943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -10995,7 +10996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -11048,7 +11049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -11101,7 +11102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -11154,7 +11155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -11207,7 +11208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -11260,7 +11261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -11313,7 +11314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -11369,7 +11370,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -11425,7 +11426,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -11478,7 +11479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -11531,7 +11532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -11584,7 +11585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -11637,7 +11638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -11690,7 +11691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -11743,7 +11744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -11796,7 +11797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -11849,7 +11850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -11905,7 +11906,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -11958,7 +11959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -12011,7 +12012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -12064,7 +12065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -12117,7 +12118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -12170,7 +12171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -12226,7 +12227,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -12279,7 +12280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -12335,7 +12336,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -12388,7 +12389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -12441,7 +12442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -12494,7 +12495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -12547,7 +12548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -12600,7 +12601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -12653,7 +12654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -12706,7 +12707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -12759,7 +12760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -12812,7 +12813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -12865,7 +12866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -12918,7 +12919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -12971,7 +12972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -13027,7 +13028,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -13080,7 +13081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -13133,7 +13134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -13186,7 +13187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -13239,7 +13240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -13292,7 +13293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -13345,7 +13346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -13398,7 +13399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -13451,7 +13452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -13504,7 +13505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -13557,7 +13558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -13610,7 +13611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -13666,7 +13667,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -13719,7 +13720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -13772,7 +13773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -13825,7 +13826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -13881,7 +13882,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -13934,7 +13935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -13987,7 +13988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -14040,7 +14041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -14093,7 +14094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -14146,7 +14147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -14199,7 +14200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -14252,7 +14253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -14305,7 +14306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -14358,7 +14359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -14411,7 +14412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -14464,7 +14465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -14520,7 +14521,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -14573,7 +14574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -14629,7 +14630,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -14682,7 +14683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -14735,7 +14736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -14788,7 +14789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -14841,7 +14842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -14894,7 +14895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -14947,7 +14948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -15000,7 +15001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -15053,7 +15054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -15106,7 +15107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -15159,7 +15160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -15215,7 +15216,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -15271,7 +15272,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -15324,7 +15325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -15377,7 +15378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -15433,7 +15434,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -15486,7 +15487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -15539,7 +15540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -15592,7 +15593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -15645,7 +15646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -15698,7 +15699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -15751,7 +15752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -15804,7 +15805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -15857,7 +15858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -15910,7 +15911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -15966,7 +15967,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -16019,7 +16020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -16075,7 +16076,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -16128,7 +16129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -16181,7 +16182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -16234,7 +16235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -16287,7 +16288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -16340,7 +16341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -16393,7 +16394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -16446,7 +16447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -16499,7 +16500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -16552,7 +16553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -16605,7 +16606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -16658,7 +16659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -16711,7 +16712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -16767,7 +16768,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -16820,7 +16821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -16873,7 +16874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -16929,7 +16930,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -16982,7 +16983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -17035,7 +17036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -17088,7 +17089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -17141,7 +17142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -17197,7 +17198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -17253,7 +17254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -17306,7 +17307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -17359,7 +17360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -17412,7 +17413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -17465,7 +17466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -17518,7 +17519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -17571,7 +17572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -17624,7 +17625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -17677,7 +17678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -17733,7 +17734,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -17786,7 +17787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -17839,7 +17840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -17892,7 +17893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -17945,7 +17946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -17998,7 +17999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -18051,7 +18052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -18104,7 +18105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -18157,7 +18158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -18210,7 +18211,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -18263,7 +18264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -18316,7 +18317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -18369,7 +18370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -18422,7 +18423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -18475,7 +18476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -18528,7 +18529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -18581,7 +18582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -18634,7 +18635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -18690,7 +18691,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -18743,7 +18744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -18796,7 +18797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -18849,7 +18850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -18902,7 +18903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -18958,7 +18959,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -19011,7 +19012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -19067,7 +19068,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -19120,7 +19121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -19173,7 +19174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -19229,7 +19230,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -19282,7 +19283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -19335,7 +19336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -19391,7 +19392,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -19447,7 +19448,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -19503,7 +19504,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -19556,7 +19557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -19612,7 +19613,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -19665,7 +19666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -19718,7 +19719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -19771,7 +19772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -19824,7 +19825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -19877,7 +19878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -19930,7 +19931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -19986,7 +19987,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -20039,7 +20040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -20092,7 +20093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -20148,7 +20149,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -20201,7 +20202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -20254,7 +20255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -20310,7 +20311,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -20366,7 +20367,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -20419,7 +20420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -20472,7 +20473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -20525,7 +20526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -20581,7 +20582,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -20634,7 +20635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -20687,7 +20688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -20740,7 +20741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -20793,7 +20794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -20846,7 +20847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -20902,7 +20903,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -20955,7 +20956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -21008,7 +21009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -21064,7 +21065,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -21117,7 +21118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>18</v>
       </c>
@@ -21173,7 +21174,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -21229,7 +21230,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>18</v>
       </c>
@@ -21285,7 +21286,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>18</v>
       </c>
@@ -21341,7 +21342,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -21394,7 +21395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -21447,7 +21448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>18</v>
       </c>
@@ -21500,7 +21501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>18</v>
       </c>
@@ -21556,7 +21557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>18</v>
       </c>
@@ -21609,7 +21610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>18</v>
       </c>
@@ -21665,7 +21666,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>18</v>
       </c>
@@ -21718,7 +21719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>18</v>
       </c>
@@ -21774,7 +21775,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>18</v>
       </c>
@@ -21827,7 +21828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -21880,7 +21881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>18</v>
       </c>
@@ -21936,7 +21937,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>18</v>
       </c>
@@ -21989,7 +21990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -22042,7 +22043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>18</v>
       </c>
@@ -22095,7 +22096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>18</v>
       </c>
@@ -22148,7 +22149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -22201,7 +22202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -22254,7 +22255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -22310,7 +22311,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -22363,7 +22364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -22419,7 +22420,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -22475,7 +22476,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -22528,7 +22529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -22581,7 +22582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -22634,7 +22635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -22690,7 +22691,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -22746,7 +22747,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -22799,7 +22800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -22852,7 +22853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -22905,7 +22906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -22958,7 +22959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -23014,7 +23015,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -23067,7 +23068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -23123,7 +23124,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -23176,7 +23177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -23229,7 +23230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -23282,7 +23283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -23335,7 +23336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -23388,7 +23389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -23441,7 +23442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -23494,7 +23495,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -23547,7 +23548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -23600,7 +23601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -23653,7 +23654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>18</v>
       </c>
@@ -23700,13 +23701,13 @@
         <v>29</v>
       </c>
       <c r="P302" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q302">
         <v>11</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="7" t="s">
         <v>18</v>
       </c>
@@ -23759,7 +23760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="7" t="s">
         <v>18</v>
       </c>
@@ -23813,6 +23814,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R304" xr:uid="{1B5C814A-1296-4077-954B-019A2A86A661}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Harpacticoida spp."/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>